--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512406_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512406_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3752</v>
+        <v>7.7052</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7741</v>
+        <v>5.4073</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6011</v>
+        <v>2.2978</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1991</v>
+        <v>5.1955</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7608</v>
+        <v>0.7516</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4383</v>
+        <v>4.4439</v>
       </c>
       <c r="J2" t="n">
-        <v>4.969</v>
+        <v>5.0427</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3191</v>
+        <v>1.3618</v>
       </c>
       <c r="L2" t="n">
-        <v>3.6499</v>
+        <v>3.681</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2301</v>
+        <v>0.1528</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5583</v>
+        <v>-0.6101</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7884</v>
+        <v>0.7629</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6432</v>
+        <v>-0.3001</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3755</v>
+        <v>-0.8256</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7322</v>
+        <v>0.5255</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0387</v>
+        <v>2.9334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9686</v>
+        <v>1.1636</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0701</v>
+        <v>1.7698</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6188</v>
+        <v>1.6316</v>
       </c>
       <c r="H3" t="n">
-        <v>0.951</v>
+        <v>0.9866</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6677</v>
+        <v>0.6451</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3051</v>
+        <v>1.3996</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8438</v>
+        <v>1.9327</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5387</v>
+        <v>-0.5331</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3136</v>
+        <v>0.2321</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8928</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2064</v>
+        <v>1.1782</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S3" t="n">
-        <v>0.381</v>
+        <v>0.193</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3512</v>
+        <v>-0.3324</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7322</v>
+        <v>0.5255</v>
       </c>
       <c r="V3" t="n">
-        <v>3.0874</v>
+        <v>3.1332</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0874</v>
+        <v>3.1332</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2364</v>
+        <v>2.3327</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9453</v>
+        <v>2.7586</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7088</v>
+        <v>-0.4259</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0982</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.089</v>
+        <v>-0.0796</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1873</v>
+        <v>0.1724</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7174</v>
+        <v>1.7834</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1102</v>
+        <v>1.1635</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6072</v>
+        <v>0.6198</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6192</v>
+        <v>-1.6905</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1992</v>
+        <v>-1.2431</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.42</v>
+        <v>-0.4474</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.465</v>
+        <v>-0.3915</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3512</v>
+        <v>-0.6439</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1138</v>
+        <v>0.2524</v>
       </c>
       <c r="V4" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6033</v>
+        <v>2.6313</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0754</v>
+        <v>1.0757</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2576</v>
+        <v>-0.0116</v>
       </c>
       <c r="F5" t="n">
-        <v>1.333</v>
+        <v>1.0872</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0987</v>
+        <v>0.0968</v>
       </c>
       <c r="H5" t="n">
-        <v>0.733</v>
+        <v>0.7315</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6343</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3978</v>
+        <v>-0.3764</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2595</v>
+        <v>0.2759</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4965</v>
+        <v>0.4733</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4736</v>
+        <v>0.4556</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0229</v>
+        <v>0.0177</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0233</v>
+        <v>-0.0212</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4501</v>
+        <v>-0.2302</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4269</v>
+        <v>0.2091</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2927</v>
+        <v>0.7315</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2927</v>
+        <v>1.5129</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2927</v>
+        <v>1.0576</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2927</v>
+        <v>1.0677</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.0101</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2927</v>
+        <v>1.7189</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2927</v>
+        <v>1.6792</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0398</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.6614</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.6115</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.0499</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.8098</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.8098</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.5407</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.4569</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.0838</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5951</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2795</v>
+        <v>0.6187</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1544</v>
+        <v>0.6522</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8749</v>
+        <v>-0.0336</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0877</v>
+        <v>1.9282</v>
       </c>
       <c r="H7" t="n">
-        <v>1.073</v>
+        <v>-1.2052</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0147</v>
+        <v>3.1334</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6983</v>
+        <v>2.2664</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6588</v>
+        <v>-0.2779</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0395</v>
+        <v>2.5443</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6106</v>
+        <v>-0.3382</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5857</v>
+        <v>-0.9273</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0248</v>
+        <v>0.5891</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8194</v>
+        <v>0.2025</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0373</v>
+        <v>0.4395</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.786</v>
+        <v>0.0864</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2514</v>
+        <v>0.3531</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5903</v>
+        <v>-0.9393</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2421</v>
+        <v>-0.6883</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8324</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2585</v>
+        <v>0.2963</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6887</v>
+        <v>0.2963</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4302</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.939</v>
+        <v>0.2963</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1932</v>
+        <v>0.2963</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1322</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2283</v>
+        <v>0.2963</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3007</v>
+        <v>0.2963</v>
       </c>
       <c r="L8" t="n">
-        <v>2.529</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2893</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8925</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8194</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2048</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0775</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1811</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1037</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9385</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6965</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3871</v>
+        <v>-0.7987</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9942</v>
+        <v>-3.3095</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6072</v>
+        <v>2.5108</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4609</v>
+        <v>-2.4578</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5184</v>
+        <v>-0.5142</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9425</v>
+        <v>-1.9436</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.5045</v>
+        <v>-3.4422</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7965</v>
+        <v>-0.7534</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.708</v>
+        <v>-2.6889</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0436</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2781</v>
+        <v>0.2392</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7655</v>
+        <v>0.7452</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6884</v>
+        <v>0.2665</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3539</v>
+        <v>-0.0452</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3345</v>
+        <v>0.3117</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SUAREZ CUSTODIO</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2237</v>
+        <v>-1.9613</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7851</v>
+        <v>-0.6754</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4386</v>
+        <v>-1.2859</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1862</v>
+        <v>-1.5752</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1647</v>
+        <v>1.0471</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0216</v>
+        <v>-2.6224</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.335</v>
+        <v>0.1556</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0585</v>
+        <v>1.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3935</v>
+        <v>-1.3444</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8512</v>
+        <v>-1.7309</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2232</v>
+        <v>-0.4529</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.628</v>
+        <v>-1.278</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2048</v>
+        <v>0.4049</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2048</v>
+        <v>1.4172</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2423</v>
+        <v>-1.1351</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4501</v>
+        <v>-1.009</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2078</v>
+        <v>-0.1262</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3442</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>P. SUAREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.411</v>
+        <v>-1.9984</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-1.5552</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4246</v>
+        <v>-0.4433</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.573</v>
+        <v>-2.2004</v>
       </c>
       <c r="H11" t="n">
-        <v>1.037</v>
+        <v>-0.1773</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6101</v>
+        <v>-2.0232</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1017</v>
+        <v>-1.3249</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4557</v>
+        <v>0.0593</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.354</v>
+        <v>-1.3842</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6747</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4186</v>
+        <v>-0.2365</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2561</v>
+        <v>-0.639</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4097</v>
+        <v>0.2025</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4339</v>
+        <v>0.2025</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5959</v>
+        <v>-0.0005</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2445</v>
+        <v>-0.2302</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3514</v>
+        <v>0.2298</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3482</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3973</v>
+        <v>-4.7547</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0598</v>
+        <v>-4.5518</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6625</v>
+        <v>-0.2029</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1222</v>
+        <v>-1.1323</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3245</v>
+        <v>-2.3133</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2022</v>
+        <v>1.1811</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1625</v>
+        <v>0.2223</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.181</v>
+        <v>-1.1294</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3435</v>
+        <v>1.3517</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2847</v>
+        <v>-1.3546</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1434</v>
+        <v>-1.184</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1413</v>
+        <v>-0.1706</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.8679</v>
+        <v>-2.8343</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1217</v>
+        <v>0.7462</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2229</v>
+        <v>-0.3809</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8988</v>
+        <v>1.1272</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5288</v>
+        <v>-1.5344</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1373</v>
+        <v>6.180400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7407000000000004</v>
+        <v>1.687399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.396800000000001</v>
+        <v>4.492600000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9919</v>
+        <v>2.9331</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5577000000000001</v>
+        <v>0.5911999999999997</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4339</v>
+        <v>2.342</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2377</v>
+        <v>7.741699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>5.720100000000001</v>
+        <v>6.108000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5177</v>
+        <v>1.6337</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.2459</v>
+        <v>-4.8085</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.162</v>
+        <v>-5.5167</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9162000000000001</v>
+        <v>0.7081999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0486</v>
+        <v>-2.0244</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.2665</v>
+        <v>-11.135</v>
       </c>
       <c r="R13" t="n">
-        <v>9.218</v>
+        <v>9.1105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.7439</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.250699999999999</v>
+        <v>-4.0679</v>
       </c>
       <c r="U13" t="n">
-        <v>3.5121</v>
+        <v>3.3243</v>
       </c>
       <c r="V13" t="n">
-        <v>5.9328</v>
+        <v>6.0154</v>
       </c>
       <c r="W13" t="n">
-        <v>9.020200000000001</v>
+        <v>9.148599999999998</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.0875</v>
+        <v>-3.1331</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0788</v>
+        <v>2.8451</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9248</v>
+        <v>4.0454</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.846</v>
+        <v>-1.2003</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6395</v>
+        <v>2.148</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8013</v>
+        <v>1.4414</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.7066</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5337</v>
+        <v>3.9331</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4151</v>
+        <v>2.3284</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1185</v>
+        <v>1.6047</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1059</v>
+        <v>-1.7851</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6138</v>
+        <v>-0.887</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7197</v>
+        <v>-0.8981</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.8221</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0242</v>
+        <v>1.8221</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2101</v>
+        <v>0.3161</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1733</v>
+        <v>-0.1387</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0368</v>
+        <v>0.4548</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7709</v>
+        <v>-1.4411</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.013</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4785</v>
+        <v>2.1671</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5757</v>
+        <v>2.853</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0972</v>
+        <v>-0.6859</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0867</v>
+        <v>3.6357</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4109</v>
+        <v>2.8067</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6758</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8075</v>
+        <v>3.5764</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2479</v>
+        <v>3.4571</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5596</v>
+        <v>0.1193</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7208</v>
+        <v>0.0593</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.837</v>
+        <v>-0.6504</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8838</v>
+        <v>0.7098</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8436</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8436</v>
+        <v>1.0123</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0291</v>
+        <v>0.3166</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4738</v>
+        <v>0.0379</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4447</v>
+        <v>0.2787</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4227</v>
+        <v>-1.7853</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6647</v>
+        <v>-2.0362</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2112</v>
+        <v>1.4122</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1238</v>
+        <v>-0.8573</v>
       </c>
       <c r="F16" t="n">
-        <v>2.335</v>
+        <v>2.2694</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3223</v>
+        <v>0.3274</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1959</v>
+        <v>-1.2053</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5182</v>
+        <v>1.5327</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2068</v>
+        <v>-0.1685</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.7323</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5427</v>
+        <v>0.5638</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5291</v>
+        <v>0.4959</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4464</v>
+        <v>-0.4731</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9755</v>
+        <v>0.9689</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.1332</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.917</v>
+        <v>-0.6888</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8431</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3482</v>
+        <v>0.3442</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3482</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.104</v>
+        <v>0.3733</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0583</v>
+        <v>0.0543</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0458</v>
+        <v>0.319</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9832</v>
+        <v>0.9841</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8282</v>
+        <v>-0.8489</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8114</v>
+        <v>1.8331</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6957</v>
+        <v>1.7589</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.047</v>
+        <v>-0.0211</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7427</v>
+        <v>1.78</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7125</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7812</v>
+        <v>-0.8278</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0687</v>
+        <v>0.0531</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6371</v>
+        <v>-0.3599</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6132</v>
+        <v>-0.6924</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0239</v>
+        <v>0.3324</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3997</v>
+        <v>-0.2643</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.037</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6373</v>
+        <v>-0.3348</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3858</v>
+        <v>-0.4162</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6748</v>
+        <v>-0.1379</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0606</v>
+        <v>-0.2783</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2268</v>
+        <v>0.1588</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0332</v>
+        <v>0.0395</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1935</v>
+        <v>0.1193</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6126</v>
+        <v>-0.5749</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6415</v>
+        <v>-0.1774</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2542</v>
+        <v>-0.3975</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6145</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4097</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.171</v>
+        <v>0.1518</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.786</v>
+        <v>-0.0883</v>
       </c>
       <c r="U18" t="n">
-        <v>0.615</v>
+        <v>0.2401</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5032</v>
+        <v>-0.356</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0389</v>
+        <v>-1.8653</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4643</v>
+        <v>1.5093</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.405</v>
+        <v>0.3867</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1284</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2766</v>
+        <v>1.0777</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1576</v>
+        <v>-0.1885</v>
       </c>
       <c r="K19" t="n">
-        <v>0.039</v>
+        <v>-0.0204</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1185</v>
+        <v>-0.168</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5625</v>
+        <v>0.5752</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1674</v>
+        <v>-0.6706</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3952</v>
+        <v>1.2458</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.4049</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0982</v>
+        <v>-0.1354</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1965</v>
+        <v>-0.6646</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0982</v>
+        <v>0.5292</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7788</v>
+        <v>-1.9329</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0714</v>
+        <v>-1.8051</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2926</v>
+        <v>-0.1278</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0246</v>
+        <v>-1.0496</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3321</v>
+        <v>-0.3547</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6926</v>
+        <v>-0.695</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1472</v>
+        <v>1.1921</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4214</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7258</v>
+        <v>0.7391</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1718</v>
+        <v>-2.2418</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7534</v>
+        <v>-0.8077</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4183</v>
+        <v>-1.4341</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0652</v>
+        <v>0.9266</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8542</v>
+        <v>0.0395</v>
       </c>
       <c r="U20" t="n">
-        <v>1.211</v>
+        <v>0.887</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>N. WILLIAMS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3354</v>
+        <v>-2.1219</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5705</v>
+        <v>-0.9066</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2352</v>
+        <v>-1.2153</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6456</v>
+        <v>-3.0922</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5574</v>
+        <v>0.5124</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0882</v>
+        <v>-3.6047</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.925</v>
+        <v>-2.0205</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1388</v>
+        <v>1.3604</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7863</v>
+        <v>-3.3809</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7205</v>
+        <v>-1.0717</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4186</v>
+        <v>-0.848</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3019</v>
+        <v>-0.2237</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0242</v>
+        <v>1.8221</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0242</v>
+        <v>1.8221</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3959</v>
+        <v>-0.2566</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7776</v>
+        <v>-0.3272</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1735</v>
+        <v>0.0706</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9385</v>
+        <v>-0.5951</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1806</v>
+        <v>1.4411</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2421</v>
+        <v>-2.0362</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4444</v>
+        <v>-2.2339</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1067</v>
+        <v>0.0225</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3377</v>
+        <v>-2.2563</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9428</v>
+        <v>-0.9738</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0756</v>
+        <v>-0.0977</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8672</v>
+        <v>-0.8761</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0794</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1308</v>
+        <v>-0.1192</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8515</v>
+        <v>-0.8943</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0552</v>
+        <v>0.0215</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1274</v>
+        <v>0.1565</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0154</v>
+        <v>0.1019</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.112</v>
+        <v>0.0546</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.6033</v>
+        <v>-2.6313</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.6033</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2544</v>
+        <v>-2.3501</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3428</v>
+        <v>-1.9384</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0884</v>
+        <v>-0.4117</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2593</v>
+        <v>-2.6314</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4606</v>
+        <v>-0.5537</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7987</v>
+        <v>-2.0777</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5325</v>
+        <v>-0.8651</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1535</v>
+        <v>-0.1008</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.379</v>
+        <v>-0.7644</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2733</v>
+        <v>-1.7663</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.307</v>
+        <v>-0.4529</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5803</v>
+        <v>-1.3134</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6145</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3806</v>
+        <v>0.3543</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.786</v>
+        <v>-0.239</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4054</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.9393</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. WILLIAMS</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2942</v>
+        <v>-3.0267</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6646</v>
+        <v>-4.1655</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6296</v>
+        <v>1.1388</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1321</v>
+        <v>-2.252</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4827</v>
+        <v>-1.4627</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.6147</v>
+        <v>-0.7893</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1131</v>
+        <v>-2.4887</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2916</v>
+        <v>-1.128</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.4048</v>
+        <v>-1.3607</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0189</v>
+        <v>0.2367</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8089</v>
+        <v>-0.3346</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.21</v>
+        <v>0.5714</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8436</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8436</v>
+        <v>0.4049</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4154</v>
+        <v>-0.1674</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9741</v>
+        <v>-0.6646</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4413</v>
+        <v>0.4972</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5903</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4227</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.137600000000001</v>
+        <v>-5.488100000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.3969</v>
+        <v>-4.492499999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7404999999999999</v>
+        <v>-0.9955999999999998</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.991899999999999</v>
+        <v>-2.933299999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5580999999999995</v>
+        <v>-0.5913999999999996</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.4338</v>
+        <v>-2.341899999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>4.246199999999999</v>
+        <v>4.8086</v>
       </c>
       <c r="K25" t="n">
-        <v>5.1622</v>
+        <v>5.516599999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9162999999999997</v>
+        <v>-0.708</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.2376</v>
+        <v>-7.741700000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.720000000000001</v>
+        <v>-6.108</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.5176</v>
+        <v>-1.633599999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.218</v>
+        <v>-9.1105</v>
       </c>
       <c r="R25" t="n">
-        <v>11.2664</v>
+        <v>11.1351</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7385000000000002</v>
+        <v>1.4358</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.5121</v>
+        <v>-3.3243</v>
       </c>
       <c r="U25" t="n">
-        <v>4.250500000000001</v>
+        <v>4.759900000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.9329</v>
+        <v>-6.015299999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>3.0875</v>
+        <v>3.1331</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.020299999999999</v>
+        <v>-9.148499999999999</v>
       </c>
     </row>
   </sheetData>
